--- a/new_agents.xlsx
+++ b/new_agents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanlavery/Desktop/re-scraper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89DCDE23-D3E5-5746-A7DA-25999153AA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3512ACA-88A6-184F-AC06-76A88557424E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16440" xr2:uid="{8FE76719-5B44-404B-BE8B-5FF02F7A1895}"/>
   </bookViews>
@@ -582,14 +582,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B5D1C4-E84E-8542-AB99-7C8ACED0A647}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -605,7 +605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -613,7 +613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -621,7 +621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -629,7 +629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -637,7 +637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -645,7 +645,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -653,7 +653,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -661,7 +661,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -669,7 +669,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
@@ -677,15 +677,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -693,7 +693,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -701,20 +701,27 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="19" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <v>540.80999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>39</v>
+      </c>
+      <c r="I16">
+        <f>I15*1.1</f>
+        <v>594.89099999999996</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="19" x14ac:dyDescent="0.25">
@@ -785,6 +792,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{DDFE6429-7542-8647-8826-D50F98E2AB65}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{8AF7B1DC-9300-F346-86D3-12DDECDD8260}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{49240439-EA16-E243-A607-6D8280960353}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
